--- a/review-results/复盘信息抓取-20260906.xlsx
+++ b/review-results/复盘信息抓取-20260906.xlsx
@@ -1122,12 +1122,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>00:15</t>
         </is>
       </c>
       <c r="D2" s="3" t="n"/>
       <c r="E2" s="3" t="n">
-        <v>406.16</v>
+        <v>414.01</v>
       </c>
       <c r="I2" s="3" t="n"/>
       <c r="M2" s="3" t="n"/>
@@ -1146,12 +1146,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>00:15</t>
+          <t>00:30</t>
         </is>
       </c>
       <c r="D3" s="3" t="n"/>
       <c r="E3" s="3" t="n">
-        <v>414.01</v>
+        <v>419.85</v>
       </c>
       <c r="I3" s="3" t="n"/>
       <c r="M3" s="3" t="n"/>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>00:30</t>
+          <t>00:45</t>
         </is>
       </c>
       <c r="D4" s="3" t="n"/>
       <c r="E4" s="3" t="n">
-        <v>419.85</v>
+        <v>413.45</v>
       </c>
       <c r="I4" s="3" t="n"/>
       <c r="M4" s="3" t="n"/>
@@ -1194,12 +1194,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>00:45</t>
+          <t>01:00</t>
         </is>
       </c>
       <c r="D5" s="3" t="n"/>
       <c r="E5" s="3" t="n">
-        <v>413.45</v>
+        <v>414.1</v>
       </c>
       <c r="H5" s="3" t="n"/>
       <c r="I5" s="3" t="n"/>
@@ -1219,12 +1219,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>01:00</t>
+          <t>01:15</t>
         </is>
       </c>
       <c r="D6" s="3" t="n"/>
       <c r="E6" s="3" t="n">
-        <v>414.1</v>
+        <v>429.1</v>
       </c>
       <c r="H6" s="3" t="n"/>
       <c r="I6" s="3" t="n"/>
@@ -1244,12 +1244,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>01:15</t>
+          <t>01:30</t>
         </is>
       </c>
       <c r="D7" s="3" t="n"/>
       <c r="E7" s="3" t="n">
-        <v>429.1</v>
+        <v>419.55</v>
       </c>
       <c r="H7" s="3" t="n"/>
       <c r="I7" s="3" t="n"/>
@@ -1269,12 +1269,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>01:30</t>
+          <t>01:45</t>
         </is>
       </c>
       <c r="D8" s="3" t="n"/>
       <c r="E8" s="3" t="n">
-        <v>419.55</v>
+        <v>419.64</v>
       </c>
       <c r="H8" s="3" t="n"/>
       <c r="I8" s="3" t="n"/>
@@ -1294,12 +1294,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>01:45</t>
+          <t>02:00</t>
         </is>
       </c>
       <c r="D9" s="3" t="n"/>
       <c r="E9" s="3" t="n">
-        <v>419.64</v>
+        <v>424.72</v>
       </c>
       <c r="H9" s="3" t="n"/>
       <c r="I9" s="3" t="n"/>
@@ -1319,12 +1319,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>02:00</t>
+          <t>02:15</t>
         </is>
       </c>
       <c r="D10" s="3" t="n"/>
       <c r="E10" s="3" t="n">
-        <v>424.72</v>
+        <v>405.39</v>
       </c>
       <c r="H10" s="3" t="n"/>
       <c r="I10" s="3" t="n"/>
@@ -1344,12 +1344,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>02:15</t>
+          <t>02:30</t>
         </is>
       </c>
       <c r="D11" s="3" t="n"/>
       <c r="E11" s="3" t="n">
-        <v>405.39</v>
+        <v>421.76</v>
       </c>
       <c r="H11" s="3" t="n"/>
       <c r="I11" s="3" t="n"/>
@@ -1369,12 +1369,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>02:30</t>
+          <t>02:45</t>
         </is>
       </c>
       <c r="D12" s="3" t="n"/>
       <c r="E12" s="3" t="n">
-        <v>421.76</v>
+        <v>413.41</v>
       </c>
       <c r="H12" s="3" t="n"/>
       <c r="I12" s="3" t="n"/>
@@ -1394,12 +1394,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>02:45</t>
+          <t>03:00</t>
         </is>
       </c>
       <c r="D13" s="3" t="n"/>
       <c r="E13" s="3" t="n">
-        <v>413.41</v>
+        <v>412.82</v>
       </c>
       <c r="H13" s="3" t="n"/>
       <c r="I13" s="3" t="n"/>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>03:00</t>
+          <t>03:15</t>
         </is>
       </c>
       <c r="D14" s="3" t="n"/>
       <c r="E14" s="3" t="n">
-        <v>412.82</v>
+        <v>414.1</v>
       </c>
       <c r="I14" s="3" t="n"/>
       <c r="M14" s="3" t="n"/>
@@ -1443,12 +1443,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>03:15</t>
+          <t>03:30</t>
         </is>
       </c>
       <c r="D15" s="3" t="n"/>
       <c r="E15" s="3" t="n">
-        <v>414.1</v>
+        <v>419.64</v>
       </c>
       <c r="I15" s="3" t="n"/>
       <c r="M15" s="3" t="n"/>
@@ -1467,12 +1467,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>03:30</t>
+          <t>03:45</t>
         </is>
       </c>
       <c r="D16" s="3" t="n"/>
       <c r="E16" s="3" t="n">
-        <v>419.64</v>
+        <v>419.55</v>
       </c>
       <c r="I16" s="3" t="n"/>
       <c r="M16" s="3" t="n"/>
@@ -1491,12 +1491,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>03:45</t>
+          <t>04:00</t>
         </is>
       </c>
       <c r="D17" s="3" t="n"/>
       <c r="E17" s="3" t="n">
-        <v>419.55</v>
+        <v>419.61</v>
       </c>
       <c r="I17" s="3" t="n"/>
       <c r="M17" s="3" t="n"/>
@@ -1515,12 +1515,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>04:00</t>
+          <t>04:15</t>
         </is>
       </c>
       <c r="D18" s="3" t="n"/>
       <c r="E18" s="3" t="n">
-        <v>419.61</v>
+        <v>426.29</v>
       </c>
       <c r="I18" s="3" t="n"/>
       <c r="M18" s="3" t="n"/>
@@ -1539,12 +1539,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>04:15</t>
+          <t>04:30</t>
         </is>
       </c>
       <c r="D19" s="3" t="n"/>
       <c r="E19" s="3" t="n">
-        <v>426.29</v>
+        <v>419.76</v>
       </c>
       <c r="H19" s="3" t="n"/>
       <c r="I19" s="3" t="n"/>
@@ -1564,12 +1564,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>04:30</t>
+          <t>04:45</t>
         </is>
       </c>
       <c r="D20" s="3" t="n"/>
       <c r="E20" s="3" t="n">
-        <v>419.76</v>
+        <v>427.67</v>
       </c>
       <c r="H20" s="3" t="n"/>
       <c r="I20" s="3" t="n"/>
@@ -1589,12 +1589,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>04:45</t>
+          <t>05:00</t>
         </is>
       </c>
       <c r="D21" s="3" t="n"/>
       <c r="E21" s="3" t="n">
-        <v>427.67</v>
+        <v>428.66</v>
       </c>
       <c r="H21" s="3" t="n"/>
       <c r="I21" s="3" t="n"/>
@@ -1614,12 +1614,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>05:00</t>
+          <t>05:15</t>
         </is>
       </c>
       <c r="D22" s="3" t="n"/>
       <c r="E22" s="3" t="n">
-        <v>428.66</v>
+        <v>1192</v>
       </c>
       <c r="H22" s="3" t="n"/>
       <c r="I22" s="3" t="n"/>
@@ -1639,7 +1639,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>05:15</t>
+          <t>05:30</t>
         </is>
       </c>
       <c r="D23" s="3" t="n"/>
@@ -1664,7 +1664,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>05:30</t>
+          <t>05:45</t>
         </is>
       </c>
       <c r="D24" s="3" t="n"/>
@@ -1689,12 +1689,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>05:45</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="D25" s="3" t="n"/>
       <c r="E25" s="3" t="n">
-        <v>1192</v>
+        <v>429.69</v>
       </c>
       <c r="H25" s="3" t="n"/>
       <c r="I25" s="3" t="n"/>
@@ -1714,12 +1714,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:15</t>
         </is>
       </c>
       <c r="D26" s="3" t="n"/>
       <c r="E26" s="3" t="n">
-        <v>429.69</v>
+        <v>433.14</v>
       </c>
       <c r="H26" s="3" t="n"/>
       <c r="I26" s="3" t="n"/>
@@ -1739,12 +1739,12 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>06:15</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="D27" s="3" t="n"/>
       <c r="E27" s="3" t="n">
-        <v>433.14</v>
+        <v>421.83</v>
       </c>
       <c r="H27" s="3" t="n"/>
       <c r="I27" s="3" t="n"/>
@@ -1764,12 +1764,12 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:45</t>
         </is>
       </c>
       <c r="D28" s="3" t="n"/>
       <c r="E28" s="3" t="n">
-        <v>421.83</v>
+        <v>420.32</v>
       </c>
       <c r="H28" s="3" t="n"/>
       <c r="I28" s="3" t="n"/>
@@ -1789,12 +1789,12 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>06:45</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="D29" s="3" t="n"/>
       <c r="E29" s="3" t="n">
-        <v>420.32</v>
+        <v>405.27</v>
       </c>
       <c r="H29" s="3" t="n"/>
       <c r="I29" s="3" t="n"/>
@@ -1814,12 +1814,12 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>07:15</t>
         </is>
       </c>
       <c r="D30" s="3" t="n"/>
       <c r="E30" s="3" t="n">
-        <v>405.27</v>
+        <v>414.01</v>
       </c>
       <c r="H30" s="3" t="n"/>
       <c r="I30" s="3" t="n"/>
@@ -1839,12 +1839,12 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>07:15</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="D31" s="3" t="n"/>
       <c r="E31" s="3" t="n">
-        <v>414.01</v>
+        <v>403.14</v>
       </c>
       <c r="H31" s="3" t="n"/>
       <c r="I31" s="3" t="n"/>
@@ -1864,12 +1864,12 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>07:45</t>
         </is>
       </c>
       <c r="D32" s="3" t="n"/>
       <c r="E32" s="3" t="n">
-        <v>403.14</v>
+        <v>391.33</v>
       </c>
       <c r="H32" s="3" t="n"/>
       <c r="I32" s="3" t="n"/>
@@ -1889,12 +1889,12 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>07:45</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="D33" s="3" t="n"/>
       <c r="E33" s="3" t="n">
-        <v>391.33</v>
+        <v>378.8</v>
       </c>
       <c r="H33" s="3" t="n"/>
       <c r="I33" s="3" t="n"/>
@@ -1914,12 +1914,12 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="D34" s="3" t="n"/>
       <c r="E34" s="3" t="n">
-        <v>378.8</v>
+        <v>370.67</v>
       </c>
       <c r="H34" s="3" t="n"/>
       <c r="I34" s="3" t="n"/>
@@ -1939,12 +1939,12 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="D35" s="3" t="n"/>
       <c r="E35" s="3" t="n">
-        <v>370.67</v>
+        <v>399.23</v>
       </c>
       <c r="H35" s="3" t="n"/>
       <c r="I35" s="3" t="n"/>
@@ -1964,12 +1964,12 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="D36" s="3" t="n"/>
       <c r="E36" s="3" t="n">
-        <v>399.23</v>
+        <v>360.64</v>
       </c>
       <c r="H36" s="3" t="n"/>
       <c r="I36" s="3" t="n"/>
@@ -1989,12 +1989,12 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="D37" s="3" t="n"/>
       <c r="E37" s="3" t="n">
-        <v>360.64</v>
+        <v>362.04</v>
       </c>
       <c r="H37" s="3" t="n"/>
       <c r="I37" s="3" t="n"/>
@@ -2014,12 +2014,12 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="D38" s="3" t="n"/>
       <c r="E38" s="3" t="n">
-        <v>362.04</v>
+        <v>365.25</v>
       </c>
       <c r="H38" s="3" t="n"/>
       <c r="I38" s="3" t="n"/>
@@ -2039,12 +2039,12 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="D39" s="3" t="n"/>
       <c r="E39" s="3" t="n">
-        <v>365.25</v>
+        <v>366.2</v>
       </c>
       <c r="H39" s="3" t="n"/>
       <c r="I39" s="3" t="n"/>
@@ -2064,7 +2064,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="D40" s="3" t="n"/>
@@ -2089,12 +2089,12 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="D41" s="3" t="n"/>
       <c r="E41" s="3" t="n">
-        <v>366.2</v>
+        <v>365.25</v>
       </c>
       <c r="H41" s="3" t="n"/>
       <c r="I41" s="3" t="n"/>
@@ -2114,12 +2114,12 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="D42" s="3" t="n"/>
       <c r="E42" s="3" t="n">
-        <v>365.25</v>
+        <v>366.79</v>
       </c>
       <c r="H42" s="3" t="n"/>
       <c r="I42" s="3" t="n"/>
@@ -2139,12 +2139,12 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="D43" s="3" t="n"/>
       <c r="E43" s="3" t="n">
-        <v>366.79</v>
+        <v>363.23</v>
       </c>
       <c r="H43" s="3" t="n"/>
       <c r="I43" s="3" t="n"/>
@@ -2164,12 +2164,12 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="D44" s="3" t="n"/>
       <c r="E44" s="3" t="n">
-        <v>363.23</v>
+        <v>362.77</v>
       </c>
       <c r="H44" s="3" t="n"/>
       <c r="I44" s="3" t="n"/>
@@ -2189,12 +2189,12 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="D45" s="3" t="n"/>
       <c r="E45" s="3" t="n">
-        <v>362.77</v>
+        <v>365.25</v>
       </c>
       <c r="H45" s="3" t="n"/>
       <c r="I45" s="3" t="n"/>
@@ -2214,12 +2214,12 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="D46" s="3" t="n"/>
       <c r="E46" s="3" t="n">
-        <v>365.25</v>
+        <v>367.27</v>
       </c>
       <c r="H46" s="3" t="n"/>
       <c r="I46" s="3" t="n"/>
@@ -2239,12 +2239,12 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="D47" s="3" t="n"/>
       <c r="E47" s="3" t="n">
-        <v>367.27</v>
+        <v>491.2</v>
       </c>
       <c r="H47" s="3" t="n"/>
       <c r="I47" s="3" t="n"/>
@@ -2264,12 +2264,12 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="D48" s="3" t="n"/>
       <c r="E48" s="3" t="n">
-        <v>491.2</v>
+        <v>397.33</v>
       </c>
       <c r="H48" s="3" t="n"/>
       <c r="I48" s="3" t="n"/>
@@ -2289,12 +2289,12 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="D49" s="3" t="n"/>
       <c r="E49" s="3" t="n">
-        <v>397.33</v>
+        <v>371.47</v>
       </c>
       <c r="H49" s="3" t="n"/>
       <c r="I49" s="3" t="n"/>
@@ -2314,12 +2314,12 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="D50" s="3" t="n"/>
       <c r="E50" s="3" t="n">
-        <v>371.47</v>
+        <v>382.55</v>
       </c>
       <c r="H50" s="3" t="n"/>
       <c r="I50" s="3" t="n"/>
@@ -2339,12 +2339,12 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="D51" s="3" t="n"/>
       <c r="E51" s="3" t="n">
-        <v>382.55</v>
+        <v>375.89</v>
       </c>
       <c r="H51" s="3" t="n"/>
       <c r="I51" s="3" t="n"/>
@@ -2364,12 +2364,12 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="D52" s="3" t="n"/>
       <c r="E52" s="3" t="n">
-        <v>375.89</v>
+        <v>383.75</v>
       </c>
       <c r="H52" s="3" t="n"/>
       <c r="I52" s="3" t="n"/>
@@ -2389,12 +2389,12 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="D53" s="3" t="n"/>
       <c r="E53" s="3" t="n">
-        <v>383.75</v>
+        <v>397.33</v>
       </c>
       <c r="H53" s="3" t="n"/>
       <c r="I53" s="3" t="n"/>
@@ -2414,12 +2414,12 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="D54" s="3" t="n"/>
       <c r="E54" s="3" t="n">
-        <v>397.33</v>
+        <v>378.35</v>
       </c>
       <c r="H54" s="3" t="n"/>
       <c r="I54" s="3" t="n"/>
@@ -2439,12 +2439,12 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="D55" s="3" t="n"/>
       <c r="E55" s="3" t="n">
-        <v>378.35</v>
+        <v>375.7</v>
       </c>
       <c r="H55" s="3" t="n"/>
       <c r="I55" s="3" t="n"/>
@@ -2464,12 +2464,12 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="D56" s="3" t="n"/>
       <c r="E56" s="3" t="n">
-        <v>375.7</v>
+        <v>368.63</v>
       </c>
       <c r="H56" s="3" t="n"/>
       <c r="I56" s="3" t="n"/>
@@ -2489,12 +2489,12 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="D57" s="3" t="n"/>
       <c r="E57" s="3" t="n">
-        <v>368.63</v>
+        <v>363.8</v>
       </c>
       <c r="H57" s="3" t="n"/>
       <c r="I57" s="3" t="n"/>
@@ -2514,12 +2514,12 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="D58" s="3" t="n"/>
       <c r="E58" s="3" t="n">
-        <v>363.8</v>
+        <v>361.89</v>
       </c>
       <c r="H58" s="3" t="n"/>
       <c r="I58" s="3" t="n"/>
@@ -2539,12 +2539,12 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="D59" s="3" t="n"/>
       <c r="E59" s="3" t="n">
-        <v>361.89</v>
+        <v>213.25</v>
       </c>
       <c r="H59" s="3" t="n"/>
       <c r="I59" s="3" t="n"/>
@@ -2564,12 +2564,12 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="D60" s="3" t="n"/>
       <c r="E60" s="3" t="n">
-        <v>213.25</v>
+        <v>370.39</v>
       </c>
       <c r="H60" s="3" t="n"/>
       <c r="I60" s="3" t="n"/>
@@ -2589,12 +2589,12 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="D61" s="3" t="n"/>
       <c r="E61" s="3" t="n">
-        <v>370.39</v>
+        <v>376.82</v>
       </c>
       <c r="H61" s="3" t="n"/>
       <c r="I61" s="3" t="n"/>
@@ -2614,12 +2614,12 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="D62" s="3" t="n"/>
       <c r="E62" s="3" t="n">
-        <v>376.82</v>
+        <v>378.66</v>
       </c>
       <c r="H62" s="3" t="n"/>
       <c r="I62" s="3" t="n"/>
@@ -2639,12 +2639,12 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="D63" s="3" t="n"/>
       <c r="E63" s="3" t="n">
-        <v>378.66</v>
+        <v>391.02</v>
       </c>
       <c r="H63" s="3" t="n"/>
       <c r="I63" s="3" t="n"/>
@@ -2664,12 +2664,12 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="D64" s="3" t="n"/>
       <c r="E64" s="3" t="n">
-        <v>391.02</v>
+        <v>399.95</v>
       </c>
       <c r="H64" s="3" t="n"/>
       <c r="I64" s="3" t="n"/>
@@ -2689,12 +2689,12 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="D65" s="3" t="n"/>
       <c r="E65" s="3" t="n">
-        <v>399.95</v>
+        <v>405.27</v>
       </c>
       <c r="H65" s="3" t="n"/>
       <c r="I65" s="3" t="n"/>
@@ -2714,12 +2714,12 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="D66" s="3" t="n"/>
       <c r="E66" s="3" t="n">
-        <v>405.27</v>
+        <v>412.32</v>
       </c>
       <c r="H66" s="3" t="n"/>
       <c r="I66" s="3" t="n"/>
@@ -2739,12 +2739,12 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="D67" s="3" t="n"/>
       <c r="E67" s="3" t="n">
-        <v>412.32</v>
+        <v>413.97</v>
       </c>
       <c r="H67" s="3" t="n"/>
       <c r="I67" s="3" t="n"/>
@@ -2764,12 +2764,12 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="D68" s="3" t="n"/>
       <c r="E68" s="3" t="n">
-        <v>413.97</v>
+        <v>412.89</v>
       </c>
       <c r="H68" s="3" t="n"/>
       <c r="I68" s="3" t="n"/>
@@ -2789,12 +2789,12 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="D69" s="3" t="n"/>
       <c r="E69" s="3" t="n">
-        <v>412.89</v>
+        <v>421.86</v>
       </c>
       <c r="H69" s="3" t="n"/>
       <c r="I69" s="3" t="n"/>
@@ -2814,12 +2814,12 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="D70" s="3" t="n"/>
       <c r="E70" s="3" t="n">
-        <v>421.86</v>
+        <v>419.39</v>
       </c>
       <c r="H70" s="3" t="n"/>
       <c r="I70" s="3" t="n"/>
@@ -2839,12 +2839,12 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="D71" s="3" t="n"/>
       <c r="E71" s="3" t="n">
-        <v>419.39</v>
+        <v>421.22</v>
       </c>
       <c r="H71" s="3" t="n"/>
       <c r="I71" s="3" t="n"/>
@@ -2864,12 +2864,12 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="D72" s="3" t="n"/>
       <c r="E72" s="3" t="n">
-        <v>421.22</v>
+        <v>420.6</v>
       </c>
       <c r="H72" s="3" t="n"/>
       <c r="I72" s="3" t="n"/>
@@ -2889,7 +2889,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="D73" s="3" t="n"/>
@@ -2914,12 +2914,12 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="D74" s="3" t="n"/>
       <c r="E74" s="3" t="n">
-        <v>420.6</v>
+        <v>403.89</v>
       </c>
       <c r="H74" s="3" t="n"/>
       <c r="I74" s="3" t="n"/>
@@ -2939,12 +2939,12 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="D75" s="3" t="n"/>
       <c r="E75" s="3" t="n">
-        <v>403.89</v>
+        <v>412.89</v>
       </c>
       <c r="H75" s="3" t="n"/>
       <c r="I75" s="3" t="n"/>
@@ -2964,12 +2964,12 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>18:45</t>
         </is>
       </c>
       <c r="D76" s="3" t="n"/>
       <c r="E76" s="3" t="n">
-        <v>412.89</v>
+        <v>410.7</v>
       </c>
       <c r="H76" s="3" t="n"/>
       <c r="I76" s="3" t="n"/>
@@ -2989,12 +2989,12 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>18:45</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="D77" s="3" t="n"/>
       <c r="E77" s="3" t="n">
-        <v>410.7</v>
+        <v>410.04</v>
       </c>
       <c r="H77" s="3" t="n"/>
       <c r="I77" s="3" t="n"/>
@@ -3014,12 +3014,12 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>19:15</t>
         </is>
       </c>
       <c r="D78" s="3" t="n"/>
       <c r="E78" s="3" t="n">
-        <v>410.04</v>
+        <v>413.14</v>
       </c>
       <c r="H78" s="3" t="n"/>
       <c r="I78" s="3" t="n"/>
@@ -3039,12 +3039,12 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>19:15</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="D79" s="3" t="n"/>
       <c r="E79" s="3" t="n">
-        <v>413.14</v>
+        <v>413.95</v>
       </c>
       <c r="H79" s="3" t="n"/>
       <c r="I79" s="3" t="n"/>
@@ -3064,12 +3064,12 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>19:45</t>
         </is>
       </c>
       <c r="D80" s="3" t="n"/>
       <c r="E80" s="3" t="n">
-        <v>413.95</v>
+        <v>403.26</v>
       </c>
       <c r="H80" s="3" t="n"/>
       <c r="I80" s="3" t="n"/>
@@ -3089,12 +3089,12 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>19:45</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="D81" s="3" t="n"/>
       <c r="E81" s="3" t="n">
-        <v>403.26</v>
+        <v>397.67</v>
       </c>
       <c r="H81" s="3" t="n"/>
       <c r="I81" s="3" t="n"/>
@@ -3114,12 +3114,12 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>20:15</t>
         </is>
       </c>
       <c r="D82" s="3" t="n"/>
       <c r="E82" s="3" t="n">
-        <v>397.67</v>
+        <v>412.77</v>
       </c>
       <c r="H82" s="3" t="n"/>
       <c r="I82" s="3" t="n"/>
@@ -3139,7 +3139,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>20:15</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="D83" s="3" t="n"/>
@@ -3164,12 +3164,12 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>20:45</t>
         </is>
       </c>
       <c r="D84" s="3" t="n"/>
       <c r="E84" s="3" t="n">
-        <v>412.77</v>
+        <v>407.26</v>
       </c>
       <c r="H84" s="3" t="n"/>
       <c r="I84" s="3" t="n"/>
@@ -3189,12 +3189,12 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>20:45</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="D85" s="3" t="n"/>
       <c r="E85" s="3" t="n">
-        <v>407.26</v>
+        <v>411.16</v>
       </c>
       <c r="H85" s="3" t="n"/>
       <c r="I85" s="3" t="n"/>
@@ -3214,12 +3214,12 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:15</t>
         </is>
       </c>
       <c r="D86" s="3" t="n"/>
       <c r="E86" s="3" t="n">
-        <v>411.16</v>
+        <v>405.54</v>
       </c>
       <c r="H86" s="3" t="n"/>
       <c r="I86" s="3" t="n"/>
@@ -3239,12 +3239,12 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>21:15</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="D87" s="3" t="n"/>
       <c r="E87" s="3" t="n">
-        <v>405.54</v>
+        <v>411</v>
       </c>
       <c r="H87" s="3" t="n"/>
       <c r="I87" s="3" t="n"/>
@@ -3264,12 +3264,12 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>21:45</t>
         </is>
       </c>
       <c r="D88" s="3" t="n"/>
       <c r="E88" s="3" t="n">
-        <v>411</v>
+        <v>411.16</v>
       </c>
       <c r="H88" s="3" t="n"/>
       <c r="I88" s="3" t="n"/>
@@ -3289,12 +3289,12 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>21:45</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="D89" s="3" t="n"/>
       <c r="E89" s="3" t="n">
-        <v>411.16</v>
+        <v>404.19</v>
       </c>
       <c r="H89" s="3" t="n"/>
       <c r="I89" s="3" t="n"/>
@@ -3314,12 +3314,12 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>22:15</t>
         </is>
       </c>
       <c r="D90" s="3" t="n"/>
       <c r="E90" s="3" t="n">
-        <v>404.19</v>
+        <v>412.16</v>
       </c>
       <c r="H90" s="3" t="n"/>
       <c r="I90" s="3" t="n"/>
@@ -3339,12 +3339,12 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>22:15</t>
+          <t>22:30</t>
         </is>
       </c>
       <c r="D91" s="3" t="n"/>
       <c r="E91" s="3" t="n">
-        <v>412.16</v>
+        <v>412.47</v>
       </c>
       <c r="H91" s="3" t="n"/>
       <c r="I91" s="3" t="n"/>
@@ -3364,12 +3364,12 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>22:30</t>
+          <t>22:45</t>
         </is>
       </c>
       <c r="D92" s="3" t="n"/>
       <c r="E92" s="3" t="n">
-        <v>412.47</v>
+        <v>413.45</v>
       </c>
       <c r="H92" s="3" t="n"/>
       <c r="I92" s="3" t="n"/>
@@ -3389,7 +3389,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>22:45</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="D93" s="3" t="n"/>
@@ -3413,12 +3413,12 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>23:15</t>
         </is>
       </c>
       <c r="D94" s="3" t="n"/>
       <c r="E94" s="3" t="n">
-        <v>413.45</v>
+        <v>412.26</v>
       </c>
       <c r="I94" s="3" t="n"/>
       <c r="M94" s="3" t="n"/>
@@ -3437,12 +3437,12 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>23:15</t>
+          <t>23:30</t>
         </is>
       </c>
       <c r="D95" s="3" t="n"/>
       <c r="E95" s="3" t="n">
-        <v>412.26</v>
+        <v>404.26</v>
       </c>
       <c r="I95" s="3" t="n"/>
       <c r="M95" s="3" t="n"/>
@@ -3461,12 +3461,12 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>23:45</t>
         </is>
       </c>
       <c r="D96" s="3" t="n"/>
       <c r="E96" s="3" t="n">
-        <v>404.26</v>
+        <v>405.27</v>
       </c>
       <c r="I96" s="3" t="n"/>
       <c r="M96" s="3" t="n"/>
@@ -3485,12 +3485,12 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>23:45</t>
+          <t>24:00</t>
         </is>
       </c>
       <c r="D97" s="3" t="n"/>
       <c r="E97" s="3" t="n">
-        <v>405.27</v>
+        <v>406.16</v>
       </c>
       <c r="H97" s="3" t="n"/>
       <c r="I97" s="3" t="n"/>

--- a/review-results/复盘信息抓取-20260906.xlsx
+++ b/review-results/复盘信息抓取-20260906.xlsx
@@ -13134,7 +13134,9 @@
       <c r="C2" s="3" t="n">
         <v>30828.2</v>
       </c>
-      <c r="D2" s="3" t="n"/>
+      <c r="D2" s="3" t="n">
+        <v>8378.66</v>
+      </c>
       <c r="E2" s="3" t="n">
         <v>0</v>
       </c>
@@ -13159,7 +13161,9 @@
       <c r="C3" s="3" t="n">
         <v>30590.9</v>
       </c>
-      <c r="D3" s="3" t="n"/>
+      <c r="D3" s="3" t="n">
+        <v>8374.08</v>
+      </c>
       <c r="E3" s="3" t="n">
         <v>0</v>
       </c>
@@ -13184,7 +13188,9 @@
       <c r="C4" s="3" t="n">
         <v>30334.9</v>
       </c>
-      <c r="D4" s="3" t="n"/>
+      <c r="D4" s="3" t="n">
+        <v>8369.469999999999</v>
+      </c>
       <c r="E4" s="3" t="n">
         <v>0</v>
       </c>
@@ -13209,7 +13215,9 @@
       <c r="C5" s="3" t="n">
         <v>29933.5</v>
       </c>
-      <c r="D5" s="3" t="n"/>
+      <c r="D5" s="3" t="n">
+        <v>8362.620000000001</v>
+      </c>
       <c r="E5" s="3" t="n">
         <v>0</v>
       </c>
@@ -13234,7 +13242,9 @@
       <c r="C6" s="3" t="n">
         <v>29695.1</v>
       </c>
-      <c r="D6" s="3" t="n"/>
+      <c r="D6" s="3" t="n">
+        <v>8356.379999999999</v>
+      </c>
       <c r="E6" s="3" t="n">
         <v>0</v>
       </c>
@@ -13259,7 +13269,9 @@
       <c r="C7" s="3" t="n">
         <v>29449.9</v>
       </c>
-      <c r="D7" s="3" t="n"/>
+      <c r="D7" s="3" t="n">
+        <v>8352.629999999999</v>
+      </c>
       <c r="E7" s="3" t="n">
         <v>0</v>
       </c>
@@ -13284,7 +13296,9 @@
       <c r="C8" s="3" t="n">
         <v>29519.2</v>
       </c>
-      <c r="D8" s="3" t="n"/>
+      <c r="D8" s="3" t="n">
+        <v>8347.17</v>
+      </c>
       <c r="E8" s="3" t="n">
         <v>0</v>
       </c>
@@ -13309,7 +13323,9 @@
       <c r="C9" s="3" t="n">
         <v>29529.2</v>
       </c>
-      <c r="D9" s="3" t="n"/>
+      <c r="D9" s="3" t="n">
+        <v>8345.58</v>
+      </c>
       <c r="E9" s="3" t="n">
         <v>0</v>
       </c>
@@ -13334,7 +13350,9 @@
       <c r="C10" s="3" t="n">
         <v>32691</v>
       </c>
-      <c r="D10" s="3" t="n"/>
+      <c r="D10" s="3" t="n">
+        <v>8339.01</v>
+      </c>
       <c r="E10" s="3" t="n">
         <v>0</v>
       </c>
@@ -13359,7 +13377,9 @@
       <c r="C11" s="3" t="n">
         <v>32066.4</v>
       </c>
-      <c r="D11" s="3" t="n"/>
+      <c r="D11" s="3" t="n">
+        <v>8333.02</v>
+      </c>
       <c r="E11" s="3" t="n">
         <v>0</v>
       </c>
@@ -13384,7 +13404,9 @@
       <c r="C12" s="3" t="n">
         <v>31685.6</v>
       </c>
-      <c r="D12" s="3" t="n"/>
+      <c r="D12" s="3" t="n">
+        <v>8327.15</v>
+      </c>
       <c r="E12" s="3" t="n">
         <v>0</v>
       </c>
@@ -13409,7 +13431,9 @@
       <c r="C13" s="3" t="n">
         <v>30842.4</v>
       </c>
-      <c r="D13" s="3" t="n"/>
+      <c r="D13" s="3" t="n">
+        <v>8323.75</v>
+      </c>
       <c r="E13" s="3" t="n">
         <v>0</v>
       </c>
@@ -13434,7 +13458,9 @@
       <c r="C14" s="3" t="n">
         <v>30532.7</v>
       </c>
-      <c r="D14" s="3" t="n"/>
+      <c r="D14" s="3" t="n">
+        <v>8321.030000000001</v>
+      </c>
       <c r="E14" s="3" t="n">
         <v>0</v>
       </c>
@@ -13459,7 +13485,9 @@
       <c r="C15" s="3" t="n">
         <v>30208.7</v>
       </c>
-      <c r="D15" s="3" t="n"/>
+      <c r="D15" s="3" t="n">
+        <v>8313.620000000001</v>
+      </c>
       <c r="E15" s="3" t="n">
         <v>0</v>
       </c>
@@ -13484,7 +13512,9 @@
       <c r="C16" s="3" t="n">
         <v>30002.9</v>
       </c>
-      <c r="D16" s="3" t="n"/>
+      <c r="D16" s="3" t="n">
+        <v>8310.780000000001</v>
+      </c>
       <c r="E16" s="3" t="n">
         <v>0</v>
       </c>
@@ -13509,7 +13539,9 @@
       <c r="C17" s="3" t="n">
         <v>29841.4</v>
       </c>
-      <c r="D17" s="3" t="n"/>
+      <c r="D17" s="3" t="n">
+        <v>8306.77</v>
+      </c>
       <c r="E17" s="3" t="n">
         <v>0</v>
       </c>
@@ -13534,7 +13566,9 @@
       <c r="C18" s="3" t="n">
         <v>29617.6</v>
       </c>
-      <c r="D18" s="3" t="n"/>
+      <c r="D18" s="3" t="n">
+        <v>8314.25</v>
+      </c>
       <c r="E18" s="3" t="n">
         <v>0</v>
       </c>
@@ -13559,7 +13593,9 @@
       <c r="C19" s="3" t="n">
         <v>29206.9</v>
       </c>
-      <c r="D19" s="3" t="n"/>
+      <c r="D19" s="3" t="n">
+        <v>8311.43</v>
+      </c>
       <c r="E19" s="3" t="n">
         <v>0</v>
       </c>
@@ -13584,7 +13620,9 @@
       <c r="C20" s="3" t="n">
         <v>29371.4</v>
       </c>
-      <c r="D20" s="3" t="n"/>
+      <c r="D20" s="3" t="n">
+        <v>8308.01</v>
+      </c>
       <c r="E20" s="3" t="n">
         <v>0</v>
       </c>
@@ -13609,7 +13647,9 @@
       <c r="C21" s="3" t="n">
         <v>29549.9</v>
       </c>
-      <c r="D21" s="3" t="n"/>
+      <c r="D21" s="3" t="n">
+        <v>8304.610000000001</v>
+      </c>
       <c r="E21" s="3" t="n">
         <v>0</v>
       </c>
@@ -13634,7 +13674,9 @@
       <c r="C22" s="3" t="n">
         <v>29860.6</v>
       </c>
-      <c r="D22" s="3" t="n"/>
+      <c r="D22" s="3" t="n">
+        <v>8304.139999999999</v>
+      </c>
       <c r="E22" s="3" t="n">
         <v>0</v>
       </c>
@@ -13659,7 +13701,9 @@
       <c r="C23" s="3" t="n">
         <v>29778.6</v>
       </c>
-      <c r="D23" s="3" t="n"/>
+      <c r="D23" s="3" t="n">
+        <v>8305.02</v>
+      </c>
       <c r="E23" s="3" t="n">
         <v>0</v>
       </c>
@@ -13684,7 +13728,9 @@
       <c r="C24" s="3" t="n">
         <v>29974.9</v>
       </c>
-      <c r="D24" s="3" t="n"/>
+      <c r="D24" s="3" t="n">
+        <v>8308.92</v>
+      </c>
       <c r="E24" s="3" t="n">
         <v>0</v>
       </c>
@@ -13709,7 +13755,9 @@
       <c r="C25" s="3" t="n">
         <v>29952.3</v>
       </c>
-      <c r="D25" s="3" t="n"/>
+      <c r="D25" s="3" t="n">
+        <v>8312.030000000001</v>
+      </c>
       <c r="E25" s="3" t="n">
         <v>51.5</v>
       </c>
@@ -13734,7 +13782,9 @@
       <c r="C26" s="3" t="n">
         <v>29842.2</v>
       </c>
-      <c r="D26" s="3" t="n"/>
+      <c r="D26" s="3" t="n">
+        <v>8086.15</v>
+      </c>
       <c r="E26" s="3" t="n">
         <v>287.9</v>
       </c>
@@ -13759,7 +13809,9 @@
       <c r="C27" s="3" t="n">
         <v>29937.6</v>
       </c>
-      <c r="D27" s="3" t="n"/>
+      <c r="D27" s="3" t="n">
+        <v>7652.84</v>
+      </c>
       <c r="E27" s="3" t="n">
         <v>724.4</v>
       </c>
@@ -13784,7 +13836,9 @@
       <c r="C28" s="3" t="n">
         <v>29858.3</v>
       </c>
-      <c r="D28" s="3" t="n"/>
+      <c r="D28" s="3" t="n">
+        <v>6968.93</v>
+      </c>
       <c r="E28" s="3" t="n">
         <v>1311.5</v>
       </c>
@@ -13809,7 +13863,9 @@
       <c r="C29" s="3" t="n">
         <v>29261.4</v>
       </c>
-      <c r="D29" s="3" t="n"/>
+      <c r="D29" s="3" t="n">
+        <v>6295.53</v>
+      </c>
       <c r="E29" s="3" t="n">
         <v>1990.6</v>
       </c>
@@ -13834,7 +13890,9 @@
       <c r="C30" s="3" t="n">
         <v>28976.1</v>
       </c>
-      <c r="D30" s="3" t="n"/>
+      <c r="D30" s="3" t="n">
+        <v>5830.52</v>
+      </c>
       <c r="E30" s="3" t="n">
         <v>2760.2</v>
       </c>
@@ -13859,7 +13917,9 @@
       <c r="C31" s="3" t="n">
         <v>28766.7</v>
       </c>
-      <c r="D31" s="3" t="n"/>
+      <c r="D31" s="3" t="n">
+        <v>5347.89</v>
+      </c>
       <c r="E31" s="3" t="n">
         <v>3688.3</v>
       </c>
@@ -13884,7 +13944,9 @@
       <c r="C32" s="3" t="n">
         <v>28405.9</v>
       </c>
-      <c r="D32" s="3" t="n"/>
+      <c r="D32" s="3" t="n">
+        <v>4884.39</v>
+      </c>
       <c r="E32" s="3" t="n">
         <v>4591.7</v>
       </c>
@@ -13909,7 +13971,9 @@
       <c r="C33" s="3" t="n">
         <v>28139</v>
       </c>
-      <c r="D33" s="3" t="n"/>
+      <c r="D33" s="3" t="n">
+        <v>4472.38</v>
+      </c>
       <c r="E33" s="3" t="n">
         <v>5455.9</v>
       </c>
@@ -13934,7 +13998,9 @@
       <c r="C34" s="3" t="n">
         <v>28321.5</v>
       </c>
-      <c r="D34" s="3" t="n"/>
+      <c r="D34" s="3" t="n">
+        <v>4120.02</v>
+      </c>
       <c r="E34" s="3" t="n">
         <v>6312.8</v>
       </c>
@@ -13959,7 +14025,9 @@
       <c r="C35" s="3" t="n">
         <v>27732.6</v>
       </c>
-      <c r="D35" s="3" t="n"/>
+      <c r="D35" s="3" t="n">
+        <v>4067.44</v>
+      </c>
       <c r="E35" s="3" t="n">
         <v>7123.1</v>
       </c>
@@ -13984,7 +14052,9 @@
       <c r="C36" s="3" t="n">
         <v>27461.6</v>
       </c>
-      <c r="D36" s="3" t="n"/>
+      <c r="D36" s="3" t="n">
+        <v>4100.66</v>
+      </c>
       <c r="E36" s="3" t="n">
         <v>7869.9</v>
       </c>
@@ -14009,7 +14079,9 @@
       <c r="C37" s="3" t="n">
         <v>27499.2</v>
       </c>
-      <c r="D37" s="3" t="n"/>
+      <c r="D37" s="3" t="n">
+        <v>4127.97</v>
+      </c>
       <c r="E37" s="3" t="n">
         <v>8583.700000000001</v>
       </c>
@@ -14034,7 +14106,9 @@
       <c r="C38" s="3" t="n">
         <v>27154.2</v>
       </c>
-      <c r="D38" s="3" t="n"/>
+      <c r="D38" s="3" t="n">
+        <v>4160.09</v>
+      </c>
       <c r="E38" s="3" t="n">
         <v>9146.299999999999</v>
       </c>
@@ -14059,7 +14133,9 @@
       <c r="C39" s="3" t="n">
         <v>27045.6</v>
       </c>
-      <c r="D39" s="3" t="n"/>
+      <c r="D39" s="3" t="n">
+        <v>4203.04</v>
+      </c>
       <c r="E39" s="3" t="n">
         <v>9535</v>
       </c>
@@ -14084,7 +14160,9 @@
       <c r="C40" s="3" t="n">
         <v>26806.6</v>
       </c>
-      <c r="D40" s="3" t="n"/>
+      <c r="D40" s="3" t="n">
+        <v>4235.81</v>
+      </c>
       <c r="E40" s="3" t="n">
         <v>10117.3</v>
       </c>
@@ -14109,7 +14187,9 @@
       <c r="C41" s="3" t="n">
         <v>26449.7</v>
       </c>
-      <c r="D41" s="3" t="n"/>
+      <c r="D41" s="3" t="n">
+        <v>4256.36</v>
+      </c>
       <c r="E41" s="3" t="n">
         <v>10521.5</v>
       </c>
@@ -14134,7 +14214,9 @@
       <c r="C42" s="3" t="n">
         <v>26379.5</v>
       </c>
-      <c r="D42" s="3" t="n"/>
+      <c r="D42" s="3" t="n">
+        <v>4285.81</v>
+      </c>
       <c r="E42" s="3" t="n">
         <v>10927.6</v>
       </c>
@@ -14159,7 +14241,9 @@
       <c r="C43" s="3" t="n">
         <v>26124.7</v>
       </c>
-      <c r="D43" s="3" t="n"/>
+      <c r="D43" s="3" t="n">
+        <v>4303.16</v>
+      </c>
       <c r="E43" s="3" t="n">
         <v>11341.2</v>
       </c>
@@ -14184,7 +14268,9 @@
       <c r="C44" s="3" t="n">
         <v>26334.8</v>
       </c>
-      <c r="D44" s="3" t="n"/>
+      <c r="D44" s="3" t="n">
+        <v>4323.39</v>
+      </c>
       <c r="E44" s="3" t="n">
         <v>11553</v>
       </c>
@@ -14209,7 +14295,9 @@
       <c r="C45" s="3" t="n">
         <v>26416.9</v>
       </c>
-      <c r="D45" s="3" t="n"/>
+      <c r="D45" s="3" t="n">
+        <v>4341.36</v>
+      </c>
       <c r="E45" s="3" t="n">
         <v>11773.6</v>
       </c>
@@ -14234,7 +14322,9 @@
       <c r="C46" s="3" t="n">
         <v>28661.6</v>
       </c>
-      <c r="D46" s="3" t="n"/>
+      <c r="D46" s="3" t="n">
+        <v>4336.2</v>
+      </c>
       <c r="E46" s="3" t="n">
         <v>12150.8</v>
       </c>
@@ -14259,7 +14349,9 @@
       <c r="C47" s="3" t="n">
         <v>28774.2</v>
       </c>
-      <c r="D47" s="3" t="n"/>
+      <c r="D47" s="3" t="n">
+        <v>4354.74</v>
+      </c>
       <c r="E47" s="3" t="n">
         <v>12269.7</v>
       </c>
@@ -14284,7 +14376,9 @@
       <c r="C48" s="3" t="n">
         <v>28180.9</v>
       </c>
-      <c r="D48" s="3" t="n"/>
+      <c r="D48" s="3" t="n">
+        <v>4350.51</v>
+      </c>
       <c r="E48" s="3" t="n">
         <v>12376.5</v>
       </c>
@@ -14309,7 +14403,9 @@
       <c r="C49" s="3" t="n">
         <v>26766.7</v>
       </c>
-      <c r="D49" s="3" t="n"/>
+      <c r="D49" s="3" t="n">
+        <v>4350.5</v>
+      </c>
       <c r="E49" s="3" t="n">
         <v>12403.2</v>
       </c>
@@ -14334,7 +14430,9 @@
       <c r="C50" s="3" t="n">
         <v>26675.1</v>
       </c>
-      <c r="D50" s="3" t="n"/>
+      <c r="D50" s="3" t="n">
+        <v>4360.91</v>
+      </c>
       <c r="E50" s="3" t="n">
         <v>12404.9</v>
       </c>
@@ -14359,7 +14457,9 @@
       <c r="C51" s="3" t="n">
         <v>26701.7</v>
       </c>
-      <c r="D51" s="3" t="n"/>
+      <c r="D51" s="3" t="n">
+        <v>4351.69</v>
+      </c>
       <c r="E51" s="3" t="n">
         <v>12328.5</v>
       </c>
@@ -14384,7 +14484,9 @@
       <c r="C52" s="3" t="n">
         <v>27146.6</v>
       </c>
-      <c r="D52" s="3" t="n"/>
+      <c r="D52" s="3" t="n">
+        <v>4364.26</v>
+      </c>
       <c r="E52" s="3" t="n">
         <v>12289.8</v>
       </c>
@@ -14409,7 +14511,9 @@
       <c r="C53" s="3" t="n">
         <v>26692.4</v>
       </c>
-      <c r="D53" s="3" t="n"/>
+      <c r="D53" s="3" t="n">
+        <v>4361.49</v>
+      </c>
       <c r="E53" s="3" t="n">
         <v>12164.8</v>
       </c>
@@ -14434,7 +14538,9 @@
       <c r="C54" s="3" t="n">
         <v>27489.5</v>
       </c>
-      <c r="D54" s="3" t="n"/>
+      <c r="D54" s="3" t="n">
+        <v>4348.82</v>
+      </c>
       <c r="E54" s="3" t="n">
         <v>12036.8</v>
       </c>
@@ -14459,7 +14565,9 @@
       <c r="C55" s="3" t="n">
         <v>27649.7</v>
       </c>
-      <c r="D55" s="3" t="n"/>
+      <c r="D55" s="3" t="n">
+        <v>4340.05</v>
+      </c>
       <c r="E55" s="3" t="n">
         <v>11870.9</v>
       </c>
@@ -14484,7 +14592,9 @@
       <c r="C56" s="3" t="n">
         <v>28154.4</v>
       </c>
-      <c r="D56" s="3" t="n"/>
+      <c r="D56" s="3" t="n">
+        <v>4325.89</v>
+      </c>
       <c r="E56" s="3" t="n">
         <v>11745.7</v>
       </c>
@@ -14509,7 +14619,9 @@
       <c r="C57" s="3" t="n">
         <v>28288.5</v>
       </c>
-      <c r="D57" s="3" t="n"/>
+      <c r="D57" s="3" t="n">
+        <v>4319.12</v>
+      </c>
       <c r="E57" s="3" t="n">
         <v>11533.1</v>
       </c>
@@ -14534,7 +14646,9 @@
       <c r="C58" s="3" t="n">
         <v>28816.9</v>
       </c>
-      <c r="D58" s="3" t="n"/>
+      <c r="D58" s="3" t="n">
+        <v>4299.6</v>
+      </c>
       <c r="E58" s="3" t="n">
         <v>11189.3</v>
       </c>
@@ -14559,7 +14673,9 @@
       <c r="C59" s="3" t="n">
         <v>29054.4</v>
       </c>
-      <c r="D59" s="3" t="n"/>
+      <c r="D59" s="3" t="n">
+        <v>4283.88</v>
+      </c>
       <c r="E59" s="3" t="n">
         <v>10749.8</v>
       </c>
@@ -14584,7 +14700,9 @@
       <c r="C60" s="3" t="n">
         <v>29697.8</v>
       </c>
-      <c r="D60" s="3" t="n"/>
+      <c r="D60" s="3" t="n">
+        <v>4270.83</v>
+      </c>
       <c r="E60" s="3" t="n">
         <v>10257.2</v>
       </c>
@@ -14609,7 +14727,9 @@
       <c r="C61" s="3" t="n">
         <v>29741.5</v>
       </c>
-      <c r="D61" s="3" t="n"/>
+      <c r="D61" s="3" t="n">
+        <v>4248.97</v>
+      </c>
       <c r="E61" s="3" t="n">
         <v>9756.299999999999</v>
       </c>
@@ -14634,7 +14754,9 @@
       <c r="C62" s="3" t="n">
         <v>30216.2</v>
       </c>
-      <c r="D62" s="3" t="n"/>
+      <c r="D62" s="3" t="n">
+        <v>4315.55</v>
+      </c>
       <c r="E62" s="3" t="n">
         <v>9174.5</v>
       </c>
@@ -14659,7 +14781,9 @@
       <c r="C63" s="3" t="n">
         <v>30937.5</v>
       </c>
-      <c r="D63" s="3" t="n"/>
+      <c r="D63" s="3" t="n">
+        <v>4692.98</v>
+      </c>
       <c r="E63" s="3" t="n">
         <v>8171.4</v>
       </c>
@@ -14684,7 +14808,9 @@
       <c r="C64" s="3" t="n">
         <v>31749.9</v>
       </c>
-      <c r="D64" s="3" t="n"/>
+      <c r="D64" s="3" t="n">
+        <v>5112.47</v>
+      </c>
       <c r="E64" s="3" t="n">
         <v>7446.5</v>
       </c>
@@ -14709,7 +14835,9 @@
       <c r="C65" s="3" t="n">
         <v>32906.9</v>
       </c>
-      <c r="D65" s="3" t="n"/>
+      <c r="D65" s="3" t="n">
+        <v>5782.03</v>
+      </c>
       <c r="E65" s="3" t="n">
         <v>6826.4</v>
       </c>
@@ -14734,7 +14862,9 @@
       <c r="C66" s="3" t="n">
         <v>33351.2</v>
       </c>
-      <c r="D66" s="3" t="n"/>
+      <c r="D66" s="3" t="n">
+        <v>6451.4</v>
+      </c>
       <c r="E66" s="3" t="n">
         <v>5693.4</v>
       </c>
@@ -14759,7 +14889,9 @@
       <c r="C67" s="3" t="n">
         <v>34277.6</v>
       </c>
-      <c r="D67" s="3" t="n"/>
+      <c r="D67" s="3" t="n">
+        <v>6912.71</v>
+      </c>
       <c r="E67" s="3" t="n">
         <v>5020.9</v>
       </c>
@@ -14784,7 +14916,9 @@
       <c r="C68" s="3" t="n">
         <v>35155.4</v>
       </c>
-      <c r="D68" s="3" t="n"/>
+      <c r="D68" s="3" t="n">
+        <v>7380.96</v>
+      </c>
       <c r="E68" s="3" t="n">
         <v>4218.4</v>
       </c>
@@ -14809,7 +14943,9 @@
       <c r="C69" s="3" t="n">
         <v>36298</v>
       </c>
-      <c r="D69" s="3" t="n"/>
+      <c r="D69" s="3" t="n">
+        <v>7842.57</v>
+      </c>
       <c r="E69" s="3" t="n">
         <v>3237.2</v>
       </c>
@@ -14834,7 +14970,9 @@
       <c r="C70" s="3" t="n">
         <v>37111.9</v>
       </c>
-      <c r="D70" s="3" t="n"/>
+      <c r="D70" s="3" t="n">
+        <v>8256.450000000001</v>
+      </c>
       <c r="E70" s="3" t="n">
         <v>2339.5</v>
       </c>
@@ -14859,7 +14997,9 @@
       <c r="C71" s="3" t="n">
         <v>37784.3</v>
       </c>
-      <c r="D71" s="3" t="n"/>
+      <c r="D71" s="3" t="n">
+        <v>8468.58</v>
+      </c>
       <c r="E71" s="3" t="n">
         <v>1663.3</v>
       </c>
@@ -14884,7 +15024,9 @@
       <c r="C72" s="3" t="n">
         <v>38378.5</v>
       </c>
-      <c r="D72" s="3" t="n"/>
+      <c r="D72" s="3" t="n">
+        <v>8434.82</v>
+      </c>
       <c r="E72" s="3" t="n">
         <v>1060.3</v>
       </c>
@@ -14909,7 +15051,9 @@
       <c r="C73" s="3" t="n">
         <v>38332.7</v>
       </c>
-      <c r="D73" s="3" t="n"/>
+      <c r="D73" s="3" t="n">
+        <v>8411.459999999999</v>
+      </c>
       <c r="E73" s="3" t="n">
         <v>641.7</v>
       </c>
@@ -14934,7 +15078,9 @@
       <c r="C74" s="3" t="n">
         <v>38433.1</v>
       </c>
-      <c r="D74" s="3" t="n"/>
+      <c r="D74" s="3" t="n">
+        <v>8396.99</v>
+      </c>
       <c r="E74" s="3" t="n">
         <v>320.2</v>
       </c>
@@ -14959,7 +15105,9 @@
       <c r="C75" s="3" t="n">
         <v>38054.9</v>
       </c>
-      <c r="D75" s="3" t="n"/>
+      <c r="D75" s="3" t="n">
+        <v>8385.129999999999</v>
+      </c>
       <c r="E75" s="3" t="n">
         <v>64.3</v>
       </c>
@@ -14984,7 +15132,9 @@
       <c r="C76" s="3" t="n">
         <v>37921.9</v>
       </c>
-      <c r="D76" s="3" t="n"/>
+      <c r="D76" s="3" t="n">
+        <v>8380.190000000001</v>
+      </c>
       <c r="E76" s="3" t="n">
         <v>0</v>
       </c>
@@ -15009,7 +15159,9 @@
       <c r="C77" s="3" t="n">
         <v>37804.5</v>
       </c>
-      <c r="D77" s="3" t="n"/>
+      <c r="D77" s="3" t="n">
+        <v>8378.85</v>
+      </c>
       <c r="E77" s="3" t="n">
         <v>0</v>
       </c>
@@ -15034,7 +15186,9 @@
       <c r="C78" s="3" t="n">
         <v>37672.4</v>
       </c>
-      <c r="D78" s="3" t="n"/>
+      <c r="D78" s="3" t="n">
+        <v>8386.74</v>
+      </c>
       <c r="E78" s="3" t="n">
         <v>0</v>
       </c>
@@ -15059,7 +15213,9 @@
       <c r="C79" s="3" t="n">
         <v>37536.9</v>
       </c>
-      <c r="D79" s="3" t="n"/>
+      <c r="D79" s="3" t="n">
+        <v>8401.35</v>
+      </c>
       <c r="E79" s="3" t="n">
         <v>0</v>
       </c>
@@ -15084,7 +15240,9 @@
       <c r="C80" s="3" t="n">
         <v>36640.5</v>
       </c>
-      <c r="D80" s="3" t="n"/>
+      <c r="D80" s="3" t="n">
+        <v>8418.450000000001</v>
+      </c>
       <c r="E80" s="3" t="n">
         <v>0</v>
       </c>
@@ -15109,7 +15267,9 @@
       <c r="C81" s="3" t="n">
         <v>36683.7</v>
       </c>
-      <c r="D81" s="3" t="n"/>
+      <c r="D81" s="3" t="n">
+        <v>8436.26</v>
+      </c>
       <c r="E81" s="3" t="n">
         <v>0</v>
       </c>
@@ -15134,7 +15294,9 @@
       <c r="C82" s="3" t="n">
         <v>36478.7</v>
       </c>
-      <c r="D82" s="3" t="n"/>
+      <c r="D82" s="3" t="n">
+        <v>8432.15</v>
+      </c>
       <c r="E82" s="3" t="n">
         <v>0</v>
       </c>
@@ -15159,7 +15321,9 @@
       <c r="C83" s="3" t="n">
         <v>35943.5</v>
       </c>
-      <c r="D83" s="3" t="n"/>
+      <c r="D83" s="3" t="n">
+        <v>8430.889999999999</v>
+      </c>
       <c r="E83" s="3" t="n">
         <v>0</v>
       </c>
@@ -15184,7 +15348,9 @@
       <c r="C84" s="3" t="n">
         <v>35996.9</v>
       </c>
-      <c r="D84" s="3" t="n"/>
+      <c r="D84" s="3" t="n">
+        <v>8429.68</v>
+      </c>
       <c r="E84" s="3" t="n">
         <v>0</v>
       </c>
@@ -15209,7 +15375,9 @@
       <c r="C85" s="3" t="n">
         <v>35405.6</v>
       </c>
-      <c r="D85" s="3" t="n"/>
+      <c r="D85" s="3" t="n">
+        <v>8428.67</v>
+      </c>
       <c r="E85" s="3" t="n">
         <v>0</v>
       </c>
@@ -15234,7 +15402,9 @@
       <c r="C86" s="3" t="n">
         <v>35153.8</v>
       </c>
-      <c r="D86" s="3" t="n"/>
+      <c r="D86" s="3" t="n">
+        <v>8401.379999999999</v>
+      </c>
       <c r="E86" s="3" t="n">
         <v>0</v>
       </c>
@@ -15259,7 +15429,9 @@
       <c r="C87" s="3" t="n">
         <v>34895.6</v>
       </c>
-      <c r="D87" s="3" t="n"/>
+      <c r="D87" s="3" t="n">
+        <v>8389.77</v>
+      </c>
       <c r="E87" s="3" t="n">
         <v>0</v>
       </c>
@@ -15284,7 +15456,9 @@
       <c r="C88" s="3" t="n">
         <v>34332.3</v>
       </c>
-      <c r="D88" s="3" t="n"/>
+      <c r="D88" s="3" t="n">
+        <v>8379.440000000001</v>
+      </c>
       <c r="E88" s="3" t="n">
         <v>0</v>
       </c>
@@ -15309,7 +15483,9 @@
       <c r="C89" s="3" t="n">
         <v>33689.7</v>
       </c>
-      <c r="D89" s="3" t="n"/>
+      <c r="D89" s="3" t="n">
+        <v>8369.549999999999</v>
+      </c>
       <c r="E89" s="3" t="n">
         <v>0</v>
       </c>
@@ -15334,7 +15510,9 @@
       <c r="C90" s="3" t="n">
         <v>33376.1</v>
       </c>
-      <c r="D90" s="3" t="n"/>
+      <c r="D90" s="3" t="n">
+        <v>8319.07</v>
+      </c>
       <c r="E90" s="3" t="n">
         <v>0</v>
       </c>
@@ -15359,7 +15537,9 @@
       <c r="C91" s="3" t="n">
         <v>32889.9</v>
       </c>
-      <c r="D91" s="3" t="n"/>
+      <c r="D91" s="3" t="n">
+        <v>8317.690000000001</v>
+      </c>
       <c r="E91" s="3" t="n">
         <v>0</v>
       </c>
@@ -15384,7 +15564,9 @@
       <c r="C92" s="3" t="n">
         <v>32352.3</v>
       </c>
-      <c r="D92" s="3" t="n"/>
+      <c r="D92" s="3" t="n">
+        <v>8315.49</v>
+      </c>
       <c r="E92" s="3" t="n">
         <v>0</v>
       </c>
@@ -15409,7 +15591,9 @@
       <c r="C93" s="3" t="n">
         <v>31691.8</v>
       </c>
-      <c r="D93" s="3" t="n"/>
+      <c r="D93" s="3" t="n">
+        <v>8313.559999999999</v>
+      </c>
       <c r="E93" s="3" t="n">
         <v>0</v>
       </c>
@@ -15434,7 +15618,9 @@
       <c r="C94" s="3" t="n">
         <v>30965.8</v>
       </c>
-      <c r="D94" s="3" t="n"/>
+      <c r="D94" s="3" t="n">
+        <v>8311.969999999999</v>
+      </c>
       <c r="E94" s="3" t="n">
         <v>0</v>
       </c>
@@ -15459,7 +15645,9 @@
       <c r="C95" s="3" t="n">
         <v>30412.7</v>
       </c>
-      <c r="D95" s="3" t="n"/>
+      <c r="D95" s="3" t="n">
+        <v>8308.309999999999</v>
+      </c>
       <c r="E95" s="3" t="n">
         <v>0</v>
       </c>
@@ -15484,7 +15672,9 @@
       <c r="C96" s="3" t="n">
         <v>29745.3</v>
       </c>
-      <c r="D96" s="3" t="n"/>
+      <c r="D96" s="3" t="n">
+        <v>8304.559999999999</v>
+      </c>
       <c r="E96" s="3" t="n">
         <v>0</v>
       </c>
@@ -15509,7 +15699,9 @@
       <c r="C97" s="3" t="n">
         <v>29764.5</v>
       </c>
-      <c r="D97" s="3" t="n"/>
+      <c r="D97" s="3" t="n">
+        <v>8300.639999999999</v>
+      </c>
       <c r="E97" s="3" t="n">
         <v>0</v>
       </c>
